--- a/data/delivery/共平面类型表.xlsx
+++ b/data/delivery/共平面类型表.xlsx
@@ -484,16 +484,12 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>aaa</t>
+          <t>test-auto-export</t>
         </is>
       </c>
     </row>
@@ -519,18 +515,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>aaa</t>
-        </is>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">

--- a/data/delivery/共平面类型表.xlsx
+++ b/data/delivery/共平面类型表.xlsx
@@ -484,14 +484,14 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>test-auto-export</t>
-        </is>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>人工录入</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -515,9 +515,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>22</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>174</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>人工录入</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
